--- a/artfynd/A 27288-2021 artfynd.xlsx
+++ b/artfynd/A 27288-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122277057</v>
       </c>
       <c r="B2" t="n">
-        <v>57380</v>
+        <v>57385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27288-2021 artfynd.xlsx
+++ b/artfynd/A 27288-2021 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100048</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryobates minor</t>

--- a/artfynd/A 27288-2021 artfynd.xlsx
+++ b/artfynd/A 27288-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122277057</v>
       </c>
       <c r="B2" t="n">
-        <v>57385</v>
+        <v>57389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100048</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 27288-2021 artfynd.xlsx
+++ b/artfynd/A 27288-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122277057</v>
       </c>
       <c r="B2" t="n">
-        <v>57389</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
